--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amelielemay/Desktop/WaterDRoP/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7238DDAD-A8FC-9647-8049-F914E62B69F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A2DF96-A6DC-FF48-9EE7-CE09FBBE4397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="500" windowWidth="27620" windowHeight="16260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7960" yWindow="700" windowWidth="27620" windowHeight="16260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Key" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6568" uniqueCount="3177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6568" uniqueCount="3183">
   <si>
     <t>CASRN</t>
   </si>
@@ -9106,9 +9106,6 @@
   </si>
   <si>
     <t>2.50091222624926</t>
-  </si>
-  <si>
-    <t>111-54-6, 111-54-6, 111-54-6, 111-54-6, NA</t>
   </si>
   <si>
     <t>EPA/600/S3-87/019, EPA/600/3-88/028, EPA/600/3-89/063, EPI Suite appendix, U.S. Agricultural Research Service PPDB</t>
@@ -10778,6 +10775,27 @@
   </si>
   <si>
     <t>WaterDRoP dataset</t>
+  </si>
+  <si>
+    <t>25606-41-1</t>
+  </si>
+  <si>
+    <t>25954-13-6</t>
+  </si>
+  <si>
+    <t>123343-16-8</t>
+  </si>
+  <si>
+    <t>137-42-8</t>
+  </si>
+  <si>
+    <t>132-67-2</t>
+  </si>
+  <si>
+    <t>111-54-6, 111-54-6, 111-54-6, 111-54-6, 12427-38-2</t>
+  </si>
+  <si>
+    <t>85-00-7</t>
   </si>
 </sst>
 </file>
@@ -11288,15 +11306,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3089</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3090</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -11304,47 +11322,47 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>3092</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3093</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>3094</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3095</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>3096</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3097</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>3098</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3099</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>3100</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3101</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -11352,12 +11370,12 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -11381,7 +11399,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="9" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -11389,7 +11407,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -11397,16 +11415,16 @@
         <v>11</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="C3" s="11"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3105</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11414,7 +11432,7 @@
         <v>383</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11424,18 +11442,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>3108</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3109</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
+        <v>3109</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>3110</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11443,7 +11461,7 @@
         <v>136</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11451,7 +11469,7 @@
         <v>140</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11459,23 +11477,23 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>3115</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3116</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11483,7 +11501,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -11491,7 +11509,7 @@
         <v>80</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -11499,39 +11517,39 @@
         <v>1494</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
+        <v>3119</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>3120</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>3121</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>3122</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>3123</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>3125</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>3126</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -11539,7 +11557,7 @@
         <v>1715</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -11547,7 +11565,7 @@
         <v>799</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -11555,15 +11573,15 @@
         <v>447</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>3130</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>3131</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -11571,7 +11589,7 @@
         <v>2924</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -11579,15 +11597,15 @@
         <v>526</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
+        <v>3133</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>3134</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>3135</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -11595,7 +11613,7 @@
         <v>817</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -11603,7 +11621,7 @@
         <v>1789</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -11611,15 +11629,15 @@
         <v>1852</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
+        <v>3138</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>3139</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>3140</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -11627,7 +11645,7 @@
         <v>1696</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -11635,7 +11653,7 @@
         <v>382</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -11643,7 +11661,7 @@
         <v>889</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -11651,7 +11669,7 @@
         <v>1967</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="C37" s="4"/>
     </row>
@@ -11660,7 +11678,7 @@
         <v>2772</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="C38" s="4"/>
     </row>
@@ -11669,7 +11687,7 @@
         <v>588</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -11677,7 +11695,7 @@
         <v>554</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="C40" s="5"/>
     </row>
@@ -11686,7 +11704,7 @@
         <v>738</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -11694,7 +11712,7 @@
         <v>2050</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -11723,25 +11741,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="10" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>1</v>
@@ -11796,7 +11814,7 @@
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -12004,7 +12022,7 @@
         <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -12082,7 +12100,7 @@
         <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12134,7 +12152,7 @@
         <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -12160,7 +12178,7 @@
         <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -12186,7 +12204,7 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -12212,7 +12230,7 @@
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -12264,7 +12282,7 @@
         <v>11</v>
       </c>
       <c r="H21" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -12290,7 +12308,7 @@
         <v>11</v>
       </c>
       <c r="H22" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -12316,7 +12334,7 @@
         <v>11</v>
       </c>
       <c r="H23" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -12342,7 +12360,7 @@
         <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -12368,7 +12386,7 @@
         <v>11</v>
       </c>
       <c r="H25" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -12394,7 +12412,7 @@
         <v>11</v>
       </c>
       <c r="H26" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -12420,7 +12438,7 @@
         <v>11</v>
       </c>
       <c r="H27" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -12446,7 +12464,7 @@
         <v>11</v>
       </c>
       <c r="H28" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -12472,7 +12490,7 @@
         <v>11</v>
       </c>
       <c r="H29" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -12498,7 +12516,7 @@
         <v>11</v>
       </c>
       <c r="H30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -12524,7 +12542,7 @@
         <v>11</v>
       </c>
       <c r="H31" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -12654,7 +12672,7 @@
         <v>11</v>
       </c>
       <c r="H36" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -12680,7 +12698,7 @@
         <v>11</v>
       </c>
       <c r="H37" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -12706,7 +12724,7 @@
         <v>11</v>
       </c>
       <c r="H38" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -12784,7 +12802,7 @@
         <v>165</v>
       </c>
       <c r="H41" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -12810,7 +12828,7 @@
         <v>11</v>
       </c>
       <c r="H42" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -12836,7 +12854,7 @@
         <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -12862,7 +12880,7 @@
         <v>11</v>
       </c>
       <c r="H44" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -12888,7 +12906,7 @@
         <v>11</v>
       </c>
       <c r="H45" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -12914,7 +12932,7 @@
         <v>11</v>
       </c>
       <c r="H46" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -12940,7 +12958,7 @@
         <v>11</v>
       </c>
       <c r="H47" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -12966,7 +12984,7 @@
         <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -13018,7 +13036,7 @@
         <v>11</v>
       </c>
       <c r="H50" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -13070,7 +13088,7 @@
         <v>11</v>
       </c>
       <c r="H52" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -13200,7 +13218,7 @@
         <v>11</v>
       </c>
       <c r="H57" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -13226,7 +13244,7 @@
         <v>11</v>
       </c>
       <c r="H58" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -13252,7 +13270,7 @@
         <v>11</v>
       </c>
       <c r="H59" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -13278,7 +13296,7 @@
         <v>11</v>
       </c>
       <c r="H60" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -13304,7 +13322,7 @@
         <v>11</v>
       </c>
       <c r="H61" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -13330,7 +13348,7 @@
         <v>11</v>
       </c>
       <c r="H62" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -13382,7 +13400,7 @@
         <v>11</v>
       </c>
       <c r="H64" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -13408,7 +13426,7 @@
         <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -13434,7 +13452,7 @@
         <v>11</v>
       </c>
       <c r="H66" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -13460,7 +13478,7 @@
         <v>11</v>
       </c>
       <c r="H67" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -13486,7 +13504,7 @@
         <v>11</v>
       </c>
       <c r="H68" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -13512,7 +13530,7 @@
         <v>11</v>
       </c>
       <c r="H69" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -13538,7 +13556,7 @@
         <v>11</v>
       </c>
       <c r="H70" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -13564,7 +13582,7 @@
         <v>11</v>
       </c>
       <c r="H71" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -13590,7 +13608,7 @@
         <v>11</v>
       </c>
       <c r="H72" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -13616,7 +13634,7 @@
         <v>11</v>
       </c>
       <c r="H73" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -13642,7 +13660,7 @@
         <v>11</v>
       </c>
       <c r="H74" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -13720,7 +13738,7 @@
         <v>11</v>
       </c>
       <c r="H77" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -13746,7 +13764,7 @@
         <v>11</v>
       </c>
       <c r="H78" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -13772,7 +13790,7 @@
         <v>11</v>
       </c>
       <c r="H79" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -13824,7 +13842,7 @@
         <v>11</v>
       </c>
       <c r="H81" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -13928,7 +13946,7 @@
         <v>11</v>
       </c>
       <c r="H85" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -13980,7 +13998,7 @@
         <v>11</v>
       </c>
       <c r="H87" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -14006,7 +14024,7 @@
         <v>11</v>
       </c>
       <c r="H88" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -14058,7 +14076,7 @@
         <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -14084,7 +14102,7 @@
         <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -14110,7 +14128,7 @@
         <v>11</v>
       </c>
       <c r="H92" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -14136,7 +14154,7 @@
         <v>11</v>
       </c>
       <c r="H93" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -14162,7 +14180,7 @@
         <v>11</v>
       </c>
       <c r="H94" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -14214,7 +14232,7 @@
         <v>11</v>
       </c>
       <c r="H96" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -14240,7 +14258,7 @@
         <v>11</v>
       </c>
       <c r="H97" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -14266,7 +14284,7 @@
         <v>11</v>
       </c>
       <c r="H98" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -14292,7 +14310,7 @@
         <v>11</v>
       </c>
       <c r="H99" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -14318,7 +14336,7 @@
         <v>11</v>
       </c>
       <c r="H100" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -14344,7 +14362,7 @@
         <v>11</v>
       </c>
       <c r="H101" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -14370,7 +14388,7 @@
         <v>11</v>
       </c>
       <c r="H102" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -14448,7 +14466,7 @@
         <v>11</v>
       </c>
       <c r="H105" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -14474,7 +14492,7 @@
         <v>11</v>
       </c>
       <c r="H106" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -14500,7 +14518,7 @@
         <v>165</v>
       </c>
       <c r="H107" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -14578,7 +14596,7 @@
         <v>11</v>
       </c>
       <c r="H110" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -14630,7 +14648,7 @@
         <v>11</v>
       </c>
       <c r="H112" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -14656,7 +14674,7 @@
         <v>11</v>
       </c>
       <c r="H113" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -14708,7 +14726,7 @@
         <v>11</v>
       </c>
       <c r="H115" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -14734,7 +14752,7 @@
         <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -14760,7 +14778,7 @@
         <v>11</v>
       </c>
       <c r="H117" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -14786,7 +14804,7 @@
         <v>11</v>
       </c>
       <c r="H118" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -14812,7 +14830,7 @@
         <v>11</v>
       </c>
       <c r="H119" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -14838,7 +14856,7 @@
         <v>11</v>
       </c>
       <c r="H120" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -14890,7 +14908,7 @@
         <v>11</v>
       </c>
       <c r="H122" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -14916,7 +14934,7 @@
         <v>11</v>
       </c>
       <c r="H123" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -14942,7 +14960,7 @@
         <v>11</v>
       </c>
       <c r="H124" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -15020,7 +15038,7 @@
         <v>11</v>
       </c>
       <c r="H127" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -15046,7 +15064,7 @@
         <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -15176,7 +15194,7 @@
         <v>11</v>
       </c>
       <c r="H133" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -15202,7 +15220,7 @@
         <v>11</v>
       </c>
       <c r="H134" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -15228,7 +15246,7 @@
         <v>11</v>
       </c>
       <c r="H135" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -15254,7 +15272,7 @@
         <v>11</v>
       </c>
       <c r="H136" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -15280,7 +15298,7 @@
         <v>11</v>
       </c>
       <c r="H137" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -15337,22 +15355,22 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B140" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C140" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="D140" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="E140" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="F140" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G140" t="s">
         <v>6</v>
@@ -15436,7 +15454,7 @@
         <v>11</v>
       </c>
       <c r="H143" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -15462,7 +15480,7 @@
         <v>11</v>
       </c>
       <c r="H144" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -15488,7 +15506,7 @@
         <v>11</v>
       </c>
       <c r="H145" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -15514,7 +15532,7 @@
         <v>11</v>
       </c>
       <c r="H146" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -15722,7 +15740,7 @@
         <v>11</v>
       </c>
       <c r="H154" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -15774,7 +15792,7 @@
         <v>11</v>
       </c>
       <c r="H156" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -15800,7 +15818,7 @@
         <v>11</v>
       </c>
       <c r="H157" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -15826,7 +15844,7 @@
         <v>11</v>
       </c>
       <c r="H158" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -15852,7 +15870,7 @@
         <v>11</v>
       </c>
       <c r="H159" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -15878,7 +15896,7 @@
         <v>11</v>
       </c>
       <c r="H160" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -15930,7 +15948,7 @@
         <v>11</v>
       </c>
       <c r="H162" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -16060,7 +16078,7 @@
         <v>11</v>
       </c>
       <c r="H167" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -16086,7 +16104,7 @@
         <v>11</v>
       </c>
       <c r="H168" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -16112,7 +16130,7 @@
         <v>11</v>
       </c>
       <c r="H169" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -16190,7 +16208,7 @@
         <v>11</v>
       </c>
       <c r="H172" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -16346,7 +16364,7 @@
         <v>11</v>
       </c>
       <c r="H178" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -16372,7 +16390,7 @@
         <v>11</v>
       </c>
       <c r="H179" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -16424,7 +16442,7 @@
         <v>11</v>
       </c>
       <c r="H181" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -16450,7 +16468,7 @@
         <v>165</v>
       </c>
       <c r="H182" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -16476,7 +16494,7 @@
         <v>11</v>
       </c>
       <c r="H183" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -16502,7 +16520,7 @@
         <v>11</v>
       </c>
       <c r="H184" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -16528,7 +16546,7 @@
         <v>11</v>
       </c>
       <c r="H185" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -16606,7 +16624,7 @@
         <v>11</v>
       </c>
       <c r="H188" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -16632,7 +16650,7 @@
         <v>11</v>
       </c>
       <c r="H189" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -16658,7 +16676,7 @@
         <v>11</v>
       </c>
       <c r="H190" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -16710,7 +16728,7 @@
         <v>11</v>
       </c>
       <c r="H192" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -16736,7 +16754,7 @@
         <v>11</v>
       </c>
       <c r="H193" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -16762,7 +16780,7 @@
         <v>11</v>
       </c>
       <c r="H194" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -16788,7 +16806,7 @@
         <v>11</v>
       </c>
       <c r="H195" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -16840,7 +16858,7 @@
         <v>11</v>
       </c>
       <c r="H197" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -16918,7 +16936,7 @@
         <v>11</v>
       </c>
       <c r="H200" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -17022,7 +17040,7 @@
         <v>11</v>
       </c>
       <c r="H204" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -17048,7 +17066,7 @@
         <v>11</v>
       </c>
       <c r="H205" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -17126,7 +17144,7 @@
         <v>11</v>
       </c>
       <c r="H208" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -17152,7 +17170,7 @@
         <v>11</v>
       </c>
       <c r="H209" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -17230,7 +17248,7 @@
         <v>11</v>
       </c>
       <c r="H212" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -17256,7 +17274,7 @@
         <v>11</v>
       </c>
       <c r="H213" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -17282,7 +17300,7 @@
         <v>11</v>
       </c>
       <c r="H214" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -17308,7 +17326,7 @@
         <v>11</v>
       </c>
       <c r="H215" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -17334,7 +17352,7 @@
         <v>11</v>
       </c>
       <c r="H216" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -17360,7 +17378,7 @@
         <v>11</v>
       </c>
       <c r="H217" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -17386,7 +17404,7 @@
         <v>11</v>
       </c>
       <c r="H218" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -17412,7 +17430,7 @@
         <v>11</v>
       </c>
       <c r="H219" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -17438,7 +17456,7 @@
         <v>11</v>
       </c>
       <c r="H220" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -17464,7 +17482,7 @@
         <v>11</v>
       </c>
       <c r="H221" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -17490,7 +17508,7 @@
         <v>11</v>
       </c>
       <c r="H222" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -17516,7 +17534,7 @@
         <v>11</v>
       </c>
       <c r="H223" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -17542,7 +17560,7 @@
         <v>11</v>
       </c>
       <c r="H224" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -17568,7 +17586,7 @@
         <v>11</v>
       </c>
       <c r="H225" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -17672,7 +17690,7 @@
         <v>11</v>
       </c>
       <c r="H229" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -17698,7 +17716,7 @@
         <v>11</v>
       </c>
       <c r="H230" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -17724,7 +17742,7 @@
         <v>11</v>
       </c>
       <c r="H231" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -17750,7 +17768,7 @@
         <v>11</v>
       </c>
       <c r="H232" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -17776,7 +17794,7 @@
         <v>11</v>
       </c>
       <c r="H233" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -17802,7 +17820,7 @@
         <v>11</v>
       </c>
       <c r="H234" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -17854,7 +17872,7 @@
         <v>11</v>
       </c>
       <c r="H236" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -17880,7 +17898,7 @@
         <v>11</v>
       </c>
       <c r="H237" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -17906,7 +17924,7 @@
         <v>11</v>
       </c>
       <c r="H238" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -17932,7 +17950,7 @@
         <v>11</v>
       </c>
       <c r="H239" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -17958,7 +17976,7 @@
         <v>165</v>
       </c>
       <c r="H240" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -17984,7 +18002,7 @@
         <v>11</v>
       </c>
       <c r="H241" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -18010,7 +18028,7 @@
         <v>11</v>
       </c>
       <c r="H242" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -18036,7 +18054,7 @@
         <v>11</v>
       </c>
       <c r="H243" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -18062,7 +18080,7 @@
         <v>11</v>
       </c>
       <c r="H244" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -18088,7 +18106,7 @@
         <v>11</v>
       </c>
       <c r="H245" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -18140,7 +18158,7 @@
         <v>11</v>
       </c>
       <c r="H247" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -18218,7 +18236,7 @@
         <v>11</v>
       </c>
       <c r="H250" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -18244,7 +18262,7 @@
         <v>11</v>
       </c>
       <c r="H251" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -18270,7 +18288,7 @@
         <v>11</v>
       </c>
       <c r="H252" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -18296,7 +18314,7 @@
         <v>11</v>
       </c>
       <c r="H253" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -18322,7 +18340,7 @@
         <v>11</v>
       </c>
       <c r="H254" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -18348,7 +18366,7 @@
         <v>11</v>
       </c>
       <c r="H255" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -18374,7 +18392,7 @@
         <v>11</v>
       </c>
       <c r="H256" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -18400,7 +18418,7 @@
         <v>11</v>
       </c>
       <c r="H257" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -18426,7 +18444,7 @@
         <v>11</v>
       </c>
       <c r="H258" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -18452,7 +18470,7 @@
         <v>11</v>
       </c>
       <c r="H259" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -18478,7 +18496,7 @@
         <v>11</v>
       </c>
       <c r="H260" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -18504,7 +18522,7 @@
         <v>11</v>
       </c>
       <c r="H261" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -18556,7 +18574,7 @@
         <v>11</v>
       </c>
       <c r="H263" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -18582,7 +18600,7 @@
         <v>11</v>
       </c>
       <c r="H264" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -18608,7 +18626,7 @@
         <v>11</v>
       </c>
       <c r="H265" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -18686,7 +18704,7 @@
         <v>11</v>
       </c>
       <c r="H268" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -18712,7 +18730,7 @@
         <v>11</v>
       </c>
       <c r="H269" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -18738,7 +18756,7 @@
         <v>11</v>
       </c>
       <c r="H270" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -18764,7 +18782,7 @@
         <v>11</v>
       </c>
       <c r="H271" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -18790,7 +18808,7 @@
         <v>11</v>
       </c>
       <c r="H272" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -18868,7 +18886,7 @@
         <v>11</v>
       </c>
       <c r="H275" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -18894,7 +18912,7 @@
         <v>11</v>
       </c>
       <c r="H276" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -18972,7 +18990,7 @@
         <v>11</v>
       </c>
       <c r="H279" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -18998,7 +19016,7 @@
         <v>11</v>
       </c>
       <c r="H280" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -19024,7 +19042,7 @@
         <v>165</v>
       </c>
       <c r="H281" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -19032,7 +19050,7 @@
         <v>1097</v>
       </c>
       <c r="B282" t="s">
-        <v>4</v>
+        <v>3176</v>
       </c>
       <c r="C282" t="s">
         <v>1098</v>
@@ -19076,7 +19094,7 @@
         <v>11</v>
       </c>
       <c r="H283" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -19102,7 +19120,7 @@
         <v>11</v>
       </c>
       <c r="H284" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -19180,7 +19198,7 @@
         <v>11</v>
       </c>
       <c r="H287" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -19206,7 +19224,7 @@
         <v>11</v>
       </c>
       <c r="H288" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -19258,7 +19276,7 @@
         <v>165</v>
       </c>
       <c r="H290" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -19284,7 +19302,7 @@
         <v>11</v>
       </c>
       <c r="H291" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -19362,7 +19380,7 @@
         <v>11</v>
       </c>
       <c r="H294" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -19466,7 +19484,7 @@
         <v>11</v>
       </c>
       <c r="H298" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -19518,7 +19536,7 @@
         <v>11</v>
       </c>
       <c r="H300" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -19648,7 +19666,7 @@
         <v>165</v>
       </c>
       <c r="H305" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -19674,7 +19692,7 @@
         <v>1185</v>
       </c>
       <c r="H306" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -19804,7 +19822,7 @@
         <v>11</v>
       </c>
       <c r="H311" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -19908,7 +19926,7 @@
         <v>11</v>
       </c>
       <c r="H315" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -19934,7 +19952,7 @@
         <v>11</v>
       </c>
       <c r="H316" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -19960,7 +19978,7 @@
         <v>11</v>
       </c>
       <c r="H317" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -19986,7 +20004,7 @@
         <v>11</v>
       </c>
       <c r="H318" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -20012,7 +20030,7 @@
         <v>11</v>
       </c>
       <c r="H319" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -20064,7 +20082,7 @@
         <v>11</v>
       </c>
       <c r="H321" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -20116,7 +20134,7 @@
         <v>11</v>
       </c>
       <c r="H323" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -20124,7 +20142,7 @@
         <v>1256</v>
       </c>
       <c r="B324" t="s">
-        <v>4</v>
+        <v>3177</v>
       </c>
       <c r="C324" t="s">
         <v>1258</v>
@@ -20558,7 +20576,7 @@
         <v>11</v>
       </c>
       <c r="H340" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -20610,7 +20628,7 @@
         <v>11</v>
       </c>
       <c r="H342" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -20636,7 +20654,7 @@
         <v>11</v>
       </c>
       <c r="H343" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -20662,7 +20680,7 @@
         <v>11</v>
       </c>
       <c r="H344" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -20688,7 +20706,7 @@
         <v>11</v>
       </c>
       <c r="H345" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -20714,7 +20732,7 @@
         <v>11</v>
       </c>
       <c r="H346" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -20740,7 +20758,7 @@
         <v>11</v>
       </c>
       <c r="H347" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -20766,7 +20784,7 @@
         <v>11</v>
       </c>
       <c r="H348" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -20792,7 +20810,7 @@
         <v>11</v>
       </c>
       <c r="H349" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -20818,7 +20836,7 @@
         <v>11</v>
       </c>
       <c r="H350" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -20844,7 +20862,7 @@
         <v>11</v>
       </c>
       <c r="H351" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -20870,7 +20888,7 @@
         <v>11</v>
       </c>
       <c r="H352" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -20896,7 +20914,7 @@
         <v>11</v>
       </c>
       <c r="H353" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -21182,7 +21200,7 @@
         <v>11</v>
       </c>
       <c r="H364" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -21208,7 +21226,7 @@
         <v>11</v>
       </c>
       <c r="H365" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -21260,7 +21278,7 @@
         <v>11</v>
       </c>
       <c r="H367" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -21286,7 +21304,7 @@
         <v>11</v>
       </c>
       <c r="H368" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -21390,7 +21408,7 @@
         <v>11</v>
       </c>
       <c r="H372" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -21572,7 +21590,7 @@
         <v>11</v>
       </c>
       <c r="H379" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -21884,7 +21902,7 @@
         <v>11</v>
       </c>
       <c r="H391" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -21910,7 +21928,7 @@
         <v>11</v>
       </c>
       <c r="H392" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -21936,7 +21954,7 @@
         <v>11</v>
       </c>
       <c r="H393" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -21962,7 +21980,7 @@
         <v>11</v>
       </c>
       <c r="H394" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -22014,7 +22032,7 @@
         <v>11</v>
       </c>
       <c r="H396" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -22066,7 +22084,7 @@
         <v>11</v>
       </c>
       <c r="H398" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -22118,7 +22136,7 @@
         <v>11</v>
       </c>
       <c r="H400" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="401" spans="1:8">
@@ -22144,7 +22162,7 @@
         <v>11</v>
       </c>
       <c r="H401" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -22196,7 +22214,7 @@
         <v>11</v>
       </c>
       <c r="H403" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -22248,7 +22266,7 @@
         <v>11</v>
       </c>
       <c r="H405" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -22274,7 +22292,7 @@
         <v>165</v>
       </c>
       <c r="H406" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -22300,7 +22318,7 @@
         <v>11</v>
       </c>
       <c r="H407" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -22404,7 +22422,7 @@
         <v>11</v>
       </c>
       <c r="H411" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -22456,7 +22474,7 @@
         <v>11</v>
       </c>
       <c r="H413" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -22508,7 +22526,7 @@
         <v>11</v>
       </c>
       <c r="H415" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -22560,7 +22578,7 @@
         <v>11</v>
       </c>
       <c r="H417" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -22716,7 +22734,7 @@
         <v>11</v>
       </c>
       <c r="H423" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -22794,7 +22812,7 @@
         <v>11</v>
       </c>
       <c r="H426" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -22846,7 +22864,7 @@
         <v>11</v>
       </c>
       <c r="H428" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="429" spans="1:8">
@@ -22872,7 +22890,7 @@
         <v>11</v>
       </c>
       <c r="H429" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="430" spans="1:8">
@@ -22898,7 +22916,7 @@
         <v>11</v>
       </c>
       <c r="H430" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -22924,7 +22942,7 @@
         <v>11</v>
       </c>
       <c r="H431" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -22976,7 +22994,7 @@
         <v>11</v>
       </c>
       <c r="H433" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -23002,7 +23020,7 @@
         <v>11</v>
       </c>
       <c r="H434" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="435" spans="1:8">
@@ -23054,7 +23072,7 @@
         <v>11</v>
       </c>
       <c r="H436" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -23106,7 +23124,7 @@
         <v>11</v>
       </c>
       <c r="H438" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -23149,10 +23167,10 @@
         <v>1716</v>
       </c>
       <c r="E440" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="F440" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="G440" t="s">
         <v>383</v>
@@ -23210,7 +23228,7 @@
         <v>11</v>
       </c>
       <c r="H442" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -23470,7 +23488,7 @@
         <v>1762</v>
       </c>
       <c r="H452" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -23652,7 +23670,7 @@
         <v>11</v>
       </c>
       <c r="H459" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -23678,7 +23696,7 @@
         <v>11</v>
       </c>
       <c r="H460" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="461" spans="1:8">
@@ -23704,7 +23722,7 @@
         <v>11</v>
       </c>
       <c r="H461" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -23730,7 +23748,7 @@
         <v>11</v>
       </c>
       <c r="H462" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -23756,7 +23774,7 @@
         <v>11</v>
       </c>
       <c r="H463" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -23782,7 +23800,7 @@
         <v>11</v>
       </c>
       <c r="H464" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="465" spans="1:8">
@@ -23808,7 +23826,7 @@
         <v>11</v>
       </c>
       <c r="H465" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -23834,7 +23852,7 @@
         <v>11</v>
       </c>
       <c r="H466" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -23860,7 +23878,7 @@
         <v>11</v>
       </c>
       <c r="H467" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -23886,7 +23904,7 @@
         <v>11</v>
       </c>
       <c r="H468" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -23912,7 +23930,7 @@
         <v>11</v>
       </c>
       <c r="H469" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -23938,7 +23956,7 @@
         <v>11</v>
       </c>
       <c r="H470" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -23964,7 +23982,7 @@
         <v>11</v>
       </c>
       <c r="H471" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -24068,7 +24086,7 @@
         <v>11</v>
       </c>
       <c r="H475" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -24120,7 +24138,7 @@
         <v>165</v>
       </c>
       <c r="H477" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -24258,7 +24276,7 @@
         <v>1889</v>
       </c>
       <c r="B483" t="s">
-        <v>4</v>
+        <v>3178</v>
       </c>
       <c r="C483" t="s">
         <v>1890</v>
@@ -24302,7 +24320,7 @@
         <v>11</v>
       </c>
       <c r="H484" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -24458,7 +24476,7 @@
         <v>11</v>
       </c>
       <c r="H490" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="491" spans="1:8">
@@ -24484,7 +24502,7 @@
         <v>11</v>
       </c>
       <c r="H491" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="492" spans="1:8">
@@ -24666,7 +24684,7 @@
         <v>11</v>
       </c>
       <c r="H498" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="499" spans="1:8">
@@ -24770,7 +24788,7 @@
         <v>11</v>
       </c>
       <c r="H502" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="503" spans="1:8">
@@ -24796,7 +24814,7 @@
         <v>11</v>
       </c>
       <c r="H503" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="504" spans="1:8">
@@ -24926,7 +24944,7 @@
         <v>11</v>
       </c>
       <c r="H508" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="509" spans="1:8">
@@ -25004,7 +25022,7 @@
         <v>11</v>
       </c>
       <c r="H511" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="512" spans="1:8">
@@ -25030,7 +25048,7 @@
         <v>11</v>
       </c>
       <c r="H512" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="513" spans="1:8">
@@ -25056,7 +25074,7 @@
         <v>11</v>
       </c>
       <c r="H513" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="514" spans="1:8">
@@ -25134,7 +25152,7 @@
         <v>11</v>
       </c>
       <c r="H516" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="517" spans="1:8">
@@ -25160,7 +25178,7 @@
         <v>2017</v>
       </c>
       <c r="H517" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="518" spans="1:8">
@@ -25186,7 +25204,7 @@
         <v>11</v>
       </c>
       <c r="H518" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="519" spans="1:8">
@@ -25212,7 +25230,7 @@
         <v>11</v>
       </c>
       <c r="H519" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="520" spans="1:8">
@@ -25290,7 +25308,7 @@
         <v>11</v>
       </c>
       <c r="H522" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="523" spans="1:8">
@@ -25298,7 +25316,7 @@
         <v>2044</v>
       </c>
       <c r="B523" t="s">
-        <v>4</v>
+        <v>3179</v>
       </c>
       <c r="C523" t="s">
         <v>2047</v>
@@ -25368,7 +25386,7 @@
         <v>11</v>
       </c>
       <c r="H525" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="526" spans="1:8">
@@ -25394,7 +25412,7 @@
         <v>11</v>
       </c>
       <c r="H526" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="527" spans="1:8">
@@ -25420,7 +25438,7 @@
         <v>11</v>
       </c>
       <c r="H527" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="528" spans="1:8">
@@ -25446,7 +25464,7 @@
         <v>11</v>
       </c>
       <c r="H528" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -25472,7 +25490,7 @@
         <v>11</v>
       </c>
       <c r="H529" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -25498,7 +25516,7 @@
         <v>11</v>
       </c>
       <c r="H530" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -25524,7 +25542,7 @@
         <v>11</v>
       </c>
       <c r="H531" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="532" spans="1:8">
@@ -25550,7 +25568,7 @@
         <v>11</v>
       </c>
       <c r="H532" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -25576,7 +25594,7 @@
         <v>11</v>
       </c>
       <c r="H533" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -25602,7 +25620,7 @@
         <v>11</v>
       </c>
       <c r="H534" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="535" spans="1:8">
@@ -25628,7 +25646,7 @@
         <v>11</v>
       </c>
       <c r="H535" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="536" spans="1:8">
@@ -25654,7 +25672,7 @@
         <v>11</v>
       </c>
       <c r="H536" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="537" spans="1:8">
@@ -25680,7 +25698,7 @@
         <v>11</v>
       </c>
       <c r="H537" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="538" spans="1:8">
@@ -25732,7 +25750,7 @@
         <v>11</v>
       </c>
       <c r="H539" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="540" spans="1:8">
@@ -25758,7 +25776,7 @@
         <v>11</v>
       </c>
       <c r="H540" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="541" spans="1:8">
@@ -25784,7 +25802,7 @@
         <v>11</v>
       </c>
       <c r="H541" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -25810,7 +25828,7 @@
         <v>11</v>
       </c>
       <c r="H542" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -25862,7 +25880,7 @@
         <v>11</v>
       </c>
       <c r="H544" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="545" spans="1:8">
@@ -26070,7 +26088,7 @@
         <v>11</v>
       </c>
       <c r="H552" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="553" spans="1:8">
@@ -26122,7 +26140,7 @@
         <v>11</v>
       </c>
       <c r="H554" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="555" spans="1:8">
@@ -26226,7 +26244,7 @@
         <v>11</v>
       </c>
       <c r="H558" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="559" spans="1:8">
@@ -26252,7 +26270,7 @@
         <v>11</v>
       </c>
       <c r="H559" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="560" spans="1:8">
@@ -26278,7 +26296,7 @@
         <v>11</v>
       </c>
       <c r="H560" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="561" spans="1:8">
@@ -26304,7 +26322,7 @@
         <v>11</v>
       </c>
       <c r="H561" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="562" spans="1:8">
@@ -26330,7 +26348,7 @@
         <v>165</v>
       </c>
       <c r="H562" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="563" spans="1:8">
@@ -26356,7 +26374,7 @@
         <v>11</v>
       </c>
       <c r="H563" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="564" spans="1:8">
@@ -26382,7 +26400,7 @@
         <v>11</v>
       </c>
       <c r="H564" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -26512,7 +26530,7 @@
         <v>11</v>
       </c>
       <c r="H569" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="570" spans="1:8">
@@ -26746,7 +26764,7 @@
         <v>165</v>
       </c>
       <c r="H578" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="579" spans="1:8">
@@ -26980,7 +26998,7 @@
         <v>2017</v>
       </c>
       <c r="H587" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="588" spans="1:8">
@@ -27032,7 +27050,7 @@
         <v>165</v>
       </c>
       <c r="H589" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="590" spans="1:8">
@@ -27084,7 +27102,7 @@
         <v>165</v>
       </c>
       <c r="H591" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="592" spans="1:8">
@@ -27240,7 +27258,7 @@
         <v>11</v>
       </c>
       <c r="H597" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="598" spans="1:8">
@@ -27292,7 +27310,7 @@
         <v>11</v>
       </c>
       <c r="H599" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="600" spans="1:8">
@@ -27318,7 +27336,7 @@
         <v>11</v>
       </c>
       <c r="H600" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="601" spans="1:8">
@@ -27344,7 +27362,7 @@
         <v>11</v>
       </c>
       <c r="H601" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="602" spans="1:8">
@@ -27578,7 +27596,7 @@
         <v>11</v>
       </c>
       <c r="H610" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="611" spans="1:8">
@@ -27708,7 +27726,7 @@
         <v>11</v>
       </c>
       <c r="H615" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="616" spans="1:8">
@@ -27786,7 +27804,7 @@
         <v>11</v>
       </c>
       <c r="H618" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="619" spans="1:8">
@@ -27812,7 +27830,7 @@
         <v>11</v>
       </c>
       <c r="H619" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="620" spans="1:8">
@@ -27838,7 +27856,7 @@
         <v>11</v>
       </c>
       <c r="H620" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="621" spans="1:8">
@@ -27864,7 +27882,7 @@
         <v>11</v>
       </c>
       <c r="H621" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="622" spans="1:8">
@@ -27890,7 +27908,7 @@
         <v>11</v>
       </c>
       <c r="H622" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="623" spans="1:8">
@@ -27916,7 +27934,7 @@
         <v>11</v>
       </c>
       <c r="H623" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="624" spans="1:8">
@@ -27942,7 +27960,7 @@
         <v>11</v>
       </c>
       <c r="H624" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="625" spans="1:8">
@@ -28098,7 +28116,7 @@
         <v>11</v>
       </c>
       <c r="H630" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="631" spans="1:8">
@@ -28176,7 +28194,7 @@
         <v>11</v>
       </c>
       <c r="H633" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="634" spans="1:8">
@@ -28202,7 +28220,7 @@
         <v>11</v>
       </c>
       <c r="H634" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="635" spans="1:8">
@@ -28228,7 +28246,7 @@
         <v>11</v>
       </c>
       <c r="H635" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="636" spans="1:8">
@@ -28254,7 +28272,7 @@
         <v>11</v>
       </c>
       <c r="H636" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="637" spans="1:8">
@@ -28306,7 +28324,7 @@
         <v>11</v>
       </c>
       <c r="H638" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="639" spans="1:8">
@@ -28488,7 +28506,7 @@
         <v>11</v>
       </c>
       <c r="H645" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="646" spans="1:8">
@@ -28592,7 +28610,7 @@
         <v>11</v>
       </c>
       <c r="H649" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="650" spans="1:8">
@@ -28644,7 +28662,7 @@
         <v>11</v>
       </c>
       <c r="H651" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="652" spans="1:8">
@@ -28670,7 +28688,7 @@
         <v>11</v>
       </c>
       <c r="H652" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="653" spans="1:8">
@@ -28696,7 +28714,7 @@
         <v>11</v>
       </c>
       <c r="H653" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="654" spans="1:8">
@@ -28748,7 +28766,7 @@
         <v>11</v>
       </c>
       <c r="H655" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="656" spans="1:8">
@@ -28774,7 +28792,7 @@
         <v>11</v>
       </c>
       <c r="H656" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="657" spans="1:8">
@@ -28826,7 +28844,7 @@
         <v>165</v>
       </c>
       <c r="H658" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -28904,7 +28922,7 @@
         <v>11</v>
       </c>
       <c r="H661" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="662" spans="1:8">
@@ -28930,7 +28948,7 @@
         <v>11</v>
       </c>
       <c r="H662" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="663" spans="1:8">
@@ -28956,7 +28974,7 @@
         <v>11</v>
       </c>
       <c r="H663" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="664" spans="1:8">
@@ -28982,7 +29000,7 @@
         <v>11</v>
       </c>
       <c r="H664" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="665" spans="1:8">
@@ -29008,7 +29026,7 @@
         <v>11</v>
       </c>
       <c r="H665" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="666" spans="1:8">
@@ -29242,7 +29260,7 @@
         <v>11</v>
       </c>
       <c r="H674" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="675" spans="1:8">
@@ -29294,7 +29312,7 @@
         <v>11</v>
       </c>
       <c r="H676" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="677" spans="1:8">
@@ -29502,7 +29520,7 @@
         <v>11</v>
       </c>
       <c r="H684" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="685" spans="1:8">
@@ -29528,7 +29546,7 @@
         <v>165</v>
       </c>
       <c r="H685" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="686" spans="1:8">
@@ -29684,7 +29702,7 @@
         <v>11</v>
       </c>
       <c r="H691" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="692" spans="1:8">
@@ -29762,7 +29780,7 @@
         <v>11</v>
       </c>
       <c r="H694" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="695" spans="1:8">
@@ -29840,7 +29858,7 @@
         <v>11</v>
       </c>
       <c r="H697" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="698" spans="1:8">
@@ -29866,7 +29884,7 @@
         <v>11</v>
       </c>
       <c r="H698" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="699" spans="1:8">
@@ -29892,7 +29910,7 @@
         <v>11</v>
       </c>
       <c r="H699" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="700" spans="1:8">
@@ -29923,22 +29941,22 @@
     </row>
     <row r="701" spans="1:8">
       <c r="A701" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B701" t="s">
         <v>4</v>
       </c>
       <c r="C701" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="D701" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="E701" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="F701" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G701" t="s">
         <v>6</v>
@@ -29996,7 +30014,7 @@
         <v>11</v>
       </c>
       <c r="H703" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="704" spans="1:8">
@@ -30022,7 +30040,7 @@
         <v>11</v>
       </c>
       <c r="H704" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="705" spans="1:8">
@@ -30048,7 +30066,7 @@
         <v>11</v>
       </c>
       <c r="H705" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="706" spans="1:8">
@@ -30126,7 +30144,7 @@
         <v>11</v>
       </c>
       <c r="H708" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="709" spans="1:8">
@@ -30134,7 +30152,7 @@
         <v>2698</v>
       </c>
       <c r="B709" t="s">
-        <v>4</v>
+        <v>3180</v>
       </c>
       <c r="C709" t="s">
         <v>2699</v>
@@ -30204,7 +30222,7 @@
         <v>11</v>
       </c>
       <c r="H711" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="712" spans="1:8">
@@ -30256,7 +30274,7 @@
         <v>2017</v>
       </c>
       <c r="H713" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="714" spans="1:8">
@@ -30282,7 +30300,7 @@
         <v>11</v>
       </c>
       <c r="H714" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="715" spans="1:8">
@@ -30308,7 +30326,7 @@
         <v>11</v>
       </c>
       <c r="H715" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="716" spans="1:8">
@@ -30334,7 +30352,7 @@
         <v>165</v>
       </c>
       <c r="H716" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="717" spans="1:8">
@@ -30360,7 +30378,7 @@
         <v>11</v>
       </c>
       <c r="H717" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="718" spans="1:8">
@@ -30386,7 +30404,7 @@
         <v>11</v>
       </c>
       <c r="H718" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="719" spans="1:8">
@@ -30438,7 +30456,7 @@
         <v>11</v>
       </c>
       <c r="H720" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="721" spans="1:8">
@@ -30568,7 +30586,7 @@
         <v>11</v>
       </c>
       <c r="H725" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="726" spans="1:8">
@@ -30672,7 +30690,7 @@
         <v>11</v>
       </c>
       <c r="H729" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="730" spans="1:8">
@@ -30698,7 +30716,7 @@
         <v>11</v>
       </c>
       <c r="H730" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="731" spans="1:8">
@@ -30750,7 +30768,7 @@
         <v>11</v>
       </c>
       <c r="H732" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="733" spans="1:8">
@@ -30828,7 +30846,7 @@
         <v>11</v>
       </c>
       <c r="H735" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="736" spans="1:8">
@@ -31062,7 +31080,7 @@
         <v>11</v>
       </c>
       <c r="H744" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="745" spans="1:8">
@@ -31426,7 +31444,7 @@
         <v>11</v>
       </c>
       <c r="H758" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="759" spans="1:8">
@@ -31452,7 +31470,7 @@
         <v>11</v>
       </c>
       <c r="H759" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="760" spans="1:8">
@@ -31478,7 +31496,7 @@
         <v>11</v>
       </c>
       <c r="H760" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="761" spans="1:8">
@@ -31504,7 +31522,7 @@
         <v>11</v>
       </c>
       <c r="H761" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="762" spans="1:8">
@@ -31530,7 +31548,7 @@
         <v>11</v>
       </c>
       <c r="H762" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="763" spans="1:8">
@@ -31582,7 +31600,7 @@
         <v>11</v>
       </c>
       <c r="H764" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="765" spans="1:8">
@@ -31634,7 +31652,7 @@
         <v>11</v>
       </c>
       <c r="H766" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="767" spans="1:8">
@@ -31946,7 +31964,7 @@
         <v>11</v>
       </c>
       <c r="H778" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="779" spans="1:8">
@@ -31972,7 +31990,7 @@
         <v>11</v>
       </c>
       <c r="H779" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="780" spans="1:8">
@@ -31998,7 +32016,7 @@
         <v>11</v>
       </c>
       <c r="H780" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="781" spans="1:8">
@@ -32076,7 +32094,7 @@
         <v>11</v>
       </c>
       <c r="H783" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="784" spans="1:8">
@@ -32180,7 +32198,7 @@
         <v>11</v>
       </c>
       <c r="H787" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="788" spans="1:8">
@@ -32232,7 +32250,7 @@
         <v>11</v>
       </c>
       <c r="H789" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="790" spans="1:8">
@@ -32310,7 +32328,7 @@
         <v>11</v>
       </c>
       <c r="H792" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="793" spans="1:8">
@@ -32336,7 +32354,7 @@
         <v>11</v>
       </c>
       <c r="H793" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="794" spans="1:8">
@@ -32362,7 +32380,7 @@
         <v>11</v>
       </c>
       <c r="H794" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="795" spans="1:8">
@@ -32370,39 +32388,39 @@
         <v>3026</v>
       </c>
       <c r="B795" t="s">
-        <v>3028</v>
+        <v>3181</v>
       </c>
       <c r="C795" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="D795" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="E795" t="s">
         <v>3027</v>
       </c>
       <c r="F795" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="G795" t="s">
         <v>16</v>
       </c>
       <c r="H795" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="796" spans="1:8">
       <c r="A796" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B796" t="s">
         <v>3033</v>
       </c>
-      <c r="B796" t="s">
+      <c r="C796" t="s">
+        <v>3035</v>
+      </c>
+      <c r="D796" t="s">
         <v>3034</v>
-      </c>
-      <c r="C796" t="s">
-        <v>3036</v>
-      </c>
-      <c r="D796" t="s">
-        <v>3035</v>
       </c>
       <c r="E796" t="s">
         <v>3</v>
@@ -32414,79 +32432,79 @@
         <v>165</v>
       </c>
       <c r="H796" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="797" spans="1:8">
       <c r="A797" t="s">
+        <v>3036</v>
+      </c>
+      <c r="B797" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C797" t="s">
+        <v>3039</v>
+      </c>
+      <c r="D797" t="s">
+        <v>3039</v>
+      </c>
+      <c r="E797" t="s">
         <v>3037</v>
       </c>
-      <c r="B797" t="s">
-        <v>3039</v>
-      </c>
-      <c r="C797" t="s">
-        <v>3040</v>
-      </c>
-      <c r="D797" t="s">
-        <v>3040</v>
-      </c>
-      <c r="E797" t="s">
-        <v>3038</v>
-      </c>
       <c r="F797" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="G797" t="s">
         <v>11</v>
       </c>
       <c r="H797" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="798" spans="1:8">
       <c r="A798" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B798" t="s">
+        <v>3042</v>
+      </c>
+      <c r="C798" t="s">
+        <v>3043</v>
+      </c>
+      <c r="D798" t="s">
+        <v>3043</v>
+      </c>
+      <c r="E798" t="s">
         <v>3041</v>
       </c>
-      <c r="B798" t="s">
-        <v>3043</v>
-      </c>
-      <c r="C798" t="s">
-        <v>3044</v>
-      </c>
-      <c r="D798" t="s">
-        <v>3044</v>
-      </c>
-      <c r="E798" t="s">
-        <v>3042</v>
-      </c>
       <c r="F798" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="G798" t="s">
         <v>11</v>
       </c>
       <c r="H798" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="799" spans="1:8">
       <c r="A799" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B799" t="s">
         <v>3045</v>
       </c>
-      <c r="B799" t="s">
+      <c r="C799" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D799" t="s">
         <v>3046</v>
-      </c>
-      <c r="C799" t="s">
-        <v>3048</v>
-      </c>
-      <c r="D799" t="s">
-        <v>3047</v>
       </c>
       <c r="E799" t="s">
         <v>722</v>
       </c>
       <c r="F799" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="G799" t="s">
         <v>6</v>
@@ -32497,16 +32515,16 @@
     </row>
     <row r="800" spans="1:8">
       <c r="A800" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B800" t="s">
         <v>3050</v>
       </c>
-      <c r="B800" t="s">
+      <c r="C800" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D800" t="s">
         <v>3051</v>
-      </c>
-      <c r="C800" t="s">
-        <v>3053</v>
-      </c>
-      <c r="D800" t="s">
-        <v>3052</v>
       </c>
       <c r="E800" t="s">
         <v>3</v>
@@ -32523,16 +32541,16 @@
     </row>
     <row r="801" spans="1:8">
       <c r="A801" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B801" t="s">
         <v>3054</v>
       </c>
-      <c r="B801" t="s">
+      <c r="C801" t="s">
         <v>3055</v>
       </c>
-      <c r="C801" t="s">
-        <v>3056</v>
-      </c>
       <c r="D801" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E801" t="s">
         <v>1152</v>
@@ -32544,73 +32562,73 @@
         <v>11</v>
       </c>
       <c r="H801" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="802" spans="1:8">
       <c r="A802" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B802" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C802" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D802" t="s">
+        <v>3059</v>
+      </c>
+      <c r="E802" t="s">
         <v>3057</v>
       </c>
-      <c r="B802" t="s">
-        <v>3059</v>
-      </c>
-      <c r="C802" t="s">
-        <v>3060</v>
-      </c>
-      <c r="D802" t="s">
-        <v>3060</v>
-      </c>
-      <c r="E802" t="s">
-        <v>3058</v>
-      </c>
       <c r="F802" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="G802" t="s">
         <v>11</v>
       </c>
       <c r="H802" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="803" spans="1:8">
       <c r="A803" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B803" t="s">
+        <v>3062</v>
+      </c>
+      <c r="C803" t="s">
+        <v>3063</v>
+      </c>
+      <c r="D803" t="s">
+        <v>3063</v>
+      </c>
+      <c r="E803" t="s">
         <v>3061</v>
       </c>
-      <c r="B803" t="s">
-        <v>3063</v>
-      </c>
-      <c r="C803" t="s">
-        <v>3064</v>
-      </c>
-      <c r="D803" t="s">
-        <v>3064</v>
-      </c>
-      <c r="E803" t="s">
-        <v>3062</v>
-      </c>
       <c r="F803" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="G803" t="s">
         <v>11</v>
       </c>
       <c r="H803" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="804" spans="1:8">
       <c r="A804" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B804" t="s">
+        <v>3182</v>
+      </c>
+      <c r="C804" t="s">
         <v>3065</v>
       </c>
-      <c r="B804" t="s">
-        <v>4</v>
-      </c>
-      <c r="C804" t="s">
-        <v>3066</v>
-      </c>
       <c r="D804" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="E804" t="s">
         <v>3</v>
@@ -32627,16 +32645,16 @@
     </row>
     <row r="805" spans="1:8">
       <c r="A805" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B805" t="s">
         <v>3067</v>
       </c>
-      <c r="B805" t="s">
+      <c r="C805" t="s">
         <v>3068</v>
       </c>
-      <c r="C805" t="s">
-        <v>3069</v>
-      </c>
       <c r="D805" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="E805" t="s">
         <v>391</v>
@@ -32648,111 +32666,111 @@
         <v>11</v>
       </c>
       <c r="H805" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="806" spans="1:8">
       <c r="A806" t="s">
+        <v>3069</v>
+      </c>
+      <c r="B806" t="s">
+        <v>3071</v>
+      </c>
+      <c r="C806" t="s">
+        <v>3072</v>
+      </c>
+      <c r="D806" t="s">
+        <v>3072</v>
+      </c>
+      <c r="E806" t="s">
         <v>3070</v>
       </c>
-      <c r="B806" t="s">
-        <v>3072</v>
-      </c>
-      <c r="C806" t="s">
+      <c r="F806" t="s">
         <v>3073</v>
       </c>
-      <c r="D806" t="s">
-        <v>3073</v>
-      </c>
-      <c r="E806" t="s">
-        <v>3071</v>
-      </c>
-      <c r="F806" t="s">
-        <v>3074</v>
-      </c>
       <c r="G806" t="s">
         <v>11</v>
       </c>
       <c r="H806" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="807" spans="1:8">
       <c r="A807" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B807" t="s">
+        <v>3076</v>
+      </c>
+      <c r="C807" t="s">
+        <v>3077</v>
+      </c>
+      <c r="D807" t="s">
+        <v>3077</v>
+      </c>
+      <c r="E807" t="s">
         <v>3075</v>
       </c>
-      <c r="B807" t="s">
-        <v>3077</v>
-      </c>
-      <c r="C807" t="s">
-        <v>3078</v>
-      </c>
-      <c r="D807" t="s">
-        <v>3078</v>
-      </c>
-      <c r="E807" t="s">
-        <v>3076</v>
-      </c>
       <c r="F807" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="G807" t="s">
         <v>11</v>
       </c>
       <c r="H807" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="808" spans="1:8">
       <c r="A808" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B808" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C808" t="s">
+        <v>3082</v>
+      </c>
+      <c r="D808" t="s">
+        <v>3081</v>
+      </c>
+      <c r="E808" t="s">
         <v>3079</v>
       </c>
-      <c r="B808" t="s">
-        <v>3081</v>
-      </c>
-      <c r="C808" t="s">
-        <v>3083</v>
-      </c>
-      <c r="D808" t="s">
-        <v>3082</v>
-      </c>
-      <c r="E808" t="s">
-        <v>3080</v>
-      </c>
       <c r="F808" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="G808" t="s">
         <v>11</v>
       </c>
       <c r="H808" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="809" spans="1:8">
       <c r="A809" t="s">
+        <v>3083</v>
+      </c>
+      <c r="B809" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C809" t="s">
+        <v>3087</v>
+      </c>
+      <c r="D809" t="s">
+        <v>3086</v>
+      </c>
+      <c r="E809" t="s">
         <v>3084</v>
       </c>
-      <c r="B809" t="s">
-        <v>3086</v>
-      </c>
-      <c r="C809" t="s">
-        <v>3088</v>
-      </c>
-      <c r="D809" t="s">
-        <v>3087</v>
-      </c>
-      <c r="E809" t="s">
-        <v>3085</v>
-      </c>
       <c r="F809" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="G809" t="s">
         <v>11</v>
       </c>
       <c r="H809" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
   </sheetData>
